--- a/outputs/fifa_team_statistics/excel_por_categoria/Discipline.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Discipline.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos limpios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen numerico" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos limpios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen numerico" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,23 +498,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>7</v>
@@ -527,30 +527,30 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>55</v>
       </c>
       <c r="E3" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -560,30 +560,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -597,26 +597,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -630,26 +630,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E6" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -659,30 +659,30 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -696,26 +696,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E8" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -725,30 +725,30 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>48</v>
+      </c>
+      <c r="E9" t="n">
+        <v>58</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>7</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>47</v>
-      </c>
-      <c r="E9" t="n">
-        <v>57</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -762,26 +762,26 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -795,26 +795,26 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -824,11 +824,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -841,13 +841,13 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -857,30 +857,30 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E13" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -894,26 +894,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -927,26 +927,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Congo DR</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -956,30 +956,30 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>44</v>
       </c>
       <c r="E16" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -989,30 +989,30 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Congo DR</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>44</v>
       </c>
       <c r="E17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -1022,30 +1022,30 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1055,30 +1055,30 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E19" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1088,24 +1088,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E20" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1125,11 +1125,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E21" t="n">
         <v>29</v>
@@ -1138,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1158,23 +1158,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E22" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>5</v>
@@ -1187,30 +1187,30 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>38</v>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1220,30 +1220,30 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E24" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
         <v>5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1253,18 +1253,18 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>37</v>
       </c>
       <c r="E25" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1286,30 +1286,30 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E26" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1323,23 +1323,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E27" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
         <v>4</v>
@@ -1356,26 +1356,26 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IR Iran</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E28" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1389,26 +1389,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D29" t="n">
+        <v>35</v>
+      </c>
+      <c r="E29" t="n">
         <v>34</v>
       </c>
-      <c r="E29" t="n">
-        <v>24</v>
-      </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1422,20 +1422,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>IR Iran</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E30" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1451,30 +1451,30 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>34</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -1484,30 +1484,30 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E32" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -1517,24 +1517,24 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E33" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1554,26 +1554,26 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E34" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1587,26 +1587,26 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E35" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1616,24 +1616,24 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>32</v>
       </c>
       <c r="E36" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1649,30 +1649,30 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="D37" t="n">
+        <v>32</v>
+      </c>
+      <c r="E37" t="n">
         <v>31</v>
       </c>
-      <c r="E37" t="n">
-        <v>23</v>
-      </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -1682,30 +1682,30 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E38" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -1715,30 +1715,30 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>31</v>
       </c>
       <c r="E39" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -1748,30 +1748,30 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E40" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -1781,30 +1781,30 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D41" t="n">
+        <v>31</v>
+      </c>
+      <c r="E41" t="n">
         <v>29</v>
       </c>
-      <c r="E41" t="n">
-        <v>36</v>
-      </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -1814,24 +1814,24 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>29</v>
       </c>
       <c r="E42" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1847,30 +1847,30 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>29</v>
       </c>
       <c r="E43" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -1880,30 +1880,30 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E44" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -1913,30 +1913,30 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>27</v>
       </c>
       <c r="E45" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -1946,30 +1946,30 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Korea Republic</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E46" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1983,14 +1983,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Korea Republic</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E47" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -2087,7 +2087,7 @@
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
@@ -2148,22 +2148,22 @@
         <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>23.79166666666667</v>
+        <v>23.875</v>
       </c>
       <c r="D2" t="n">
-        <v>13.92679696695781</v>
+        <v>13.91405993338347</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>12.75</v>
+        <v>12.5</v>
       </c>
       <c r="G2" t="n">
         <v>24</v>
       </c>
       <c r="H2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I2" t="n">
         <v>48</v>
@@ -2179,25 +2179,25 @@
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>37.35416666666666</v>
+        <v>38.47916666666666</v>
       </c>
       <c r="D3" t="n">
-        <v>9.288495706101688</v>
+        <v>9.660160747821894</v>
       </c>
       <c r="E3" t="n">
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="H3" t="n">
-        <v>44.25</v>
+        <v>45.25</v>
       </c>
       <c r="I3" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -2210,22 +2210,22 @@
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>35.6875</v>
+        <v>36.75</v>
       </c>
       <c r="D4" t="n">
-        <v>10.02795295289781</v>
+        <v>10.47489399733091</v>
       </c>
       <c r="E4" t="n">
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>29.75</v>
       </c>
       <c r="G4" t="n">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
       <c r="H4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I4" t="n">
         <v>64</v>
@@ -2272,10 +2272,10 @@
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>5.666666666666667</v>
+        <v>5.8125</v>
       </c>
       <c r="D6" t="n">
-        <v>2.934268065125302</v>
+        <v>3.050331338821366</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -2284,7 +2284,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -2303,10 +2303,10 @@
         <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2291666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5152806850612228</v>
+        <v>0.5259237061407777</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2334,16 +2334,16 @@
         <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>4.083333333333333</v>
+        <v>4.145833333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>1.944258687513478</v>
+        <v>1.945967826080854</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>4</v>

--- a/outputs/fifa_team_statistics/excel_por_categoria/Discipline.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Discipline.xlsx
@@ -426,62 +426,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Fouls Against</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Fouls For</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Fouls Against</t>
+          <t>Indirect Red Cards</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Fouls For</t>
+          <t>Offsides</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Indirect Red Cards</t>
+          <t>Red Cards</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Offsides</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Red Cards</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Yellow Cards</t>
         </is>
@@ -490,649 +478,495 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>59</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>33</v>
+      </c>
+      <c r="C3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>55</v>
-      </c>
-      <c r="E3" t="n">
-        <v>43</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="C4" t="n">
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="C5" t="n">
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
+        <v>51</v>
+      </c>
+      <c r="C6" t="n">
+        <v>45</v>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
+        <v>59</v>
+      </c>
+      <c r="C7" t="n">
+        <v>37</v>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>44</v>
+      </c>
+      <c r="C8" t="n">
+        <v>48</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>7</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>49</v>
-      </c>
-      <c r="E8" t="n">
-        <v>37</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="C9" t="n">
+        <v>35</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
+        <v>48</v>
+      </c>
+      <c r="C10" t="n">
+        <v>58</v>
       </c>
       <c r="D10" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
+        <v>35</v>
+      </c>
+      <c r="C11" t="n">
+        <v>34</v>
       </c>
       <c r="D11" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Congo DR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
+        <v>44</v>
+      </c>
+      <c r="C12" t="n">
+        <v>44</v>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="C13" t="n">
+        <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="C14" t="n">
+        <v>31</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>11</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
+        <v>37</v>
+      </c>
+      <c r="C15" t="n">
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+        <v>29</v>
+      </c>
+      <c r="C16" t="n">
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Congo DR</t>
-        </is>
+        <v>49</v>
+      </c>
+      <c r="C17" t="n">
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>9</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="C18" t="n">
+        <v>42</v>
       </c>
       <c r="D18" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
+        <v>47</v>
+      </c>
+      <c r="C19" t="n">
+        <v>64</v>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
+        <v>38</v>
+      </c>
+      <c r="C20" t="n">
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
+        <v>51</v>
+      </c>
+      <c r="C21" t="n">
+        <v>42</v>
       </c>
       <c r="D21" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1140,65 +974,49 @@
       <c r="G21" t="n">
         <v>3</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Scotland</t>
-        </is>
+        <v>46</v>
+      </c>
+      <c r="C22" t="n">
+        <v>33</v>
       </c>
       <c r="D22" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
+        <v>55</v>
+      </c>
+      <c r="C23" t="n">
+        <v>43</v>
       </c>
       <c r="D23" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1206,692 +1024,524 @@
       <c r="G23" t="n">
         <v>7</v>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>IR Iran</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
+        <v>35</v>
+      </c>
+      <c r="C24" t="n">
+        <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>8</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Czechia</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="C25" t="n">
+        <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
+        <v>55</v>
+      </c>
+      <c r="C26" t="n">
+        <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="C27" t="n">
+        <v>23</v>
       </c>
       <c r="D27" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I27" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Korea Republic</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="C28" t="n">
+        <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>10</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
+        <v>44</v>
+      </c>
+      <c r="C29" t="n">
+        <v>42</v>
       </c>
       <c r="D29" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>13</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>IR Iran</t>
-        </is>
+        <v>47</v>
+      </c>
+      <c r="C30" t="n">
+        <v>57</v>
       </c>
       <c r="D30" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>30</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
+        <v>44</v>
+      </c>
+      <c r="C31" t="n">
+        <v>43</v>
       </c>
       <c r="D31" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>30</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="C32" t="n">
+        <v>23</v>
       </c>
       <c r="D32" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>30</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="C33" t="n">
+        <v>29</v>
       </c>
       <c r="D33" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>6</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>46</v>
+      </c>
+      <c r="C34" t="n">
         <v>33</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
       <c r="D34" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>8</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>33</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
+        <v>53</v>
+      </c>
+      <c r="C35" t="n">
+        <v>50</v>
       </c>
       <c r="D35" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
+        <v>29</v>
+      </c>
+      <c r="C36" t="n">
+        <v>34</v>
       </c>
       <c r="D36" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>6</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>35</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
+        <v>36</v>
+      </c>
+      <c r="C37" t="n">
+        <v>28</v>
       </c>
       <c r="D37" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>35</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
+        <v>29</v>
+      </c>
+      <c r="C38" t="n">
+        <v>26</v>
       </c>
       <c r="D38" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>38</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="C39" t="n">
+        <v>39</v>
       </c>
       <c r="D39" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>38</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
+        <v>36</v>
+      </c>
+      <c r="C40" t="n">
+        <v>48</v>
       </c>
       <c r="D40" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>7</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>38</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
+      <c r="C41" t="n">
+        <v>46</v>
       </c>
       <c r="D41" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>14</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="C42" t="n">
+        <v>15</v>
       </c>
       <c r="D42" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>41</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
+        <v>43</v>
+      </c>
+      <c r="C43" t="n">
+        <v>50</v>
       </c>
       <c r="D43" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>7</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>41</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
+        <v>37</v>
+      </c>
+      <c r="C44" t="n">
+        <v>42</v>
       </c>
       <c r="D44" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1899,32 +1549,24 @@
       <c r="G44" t="n">
         <v>3</v>
       </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>44</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Iraq</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="C45" t="n">
+        <v>34</v>
       </c>
       <c r="D45" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -1932,142 +1574,104 @@
       <c r="G45" t="n">
         <v>1</v>
       </c>
-      <c r="H45" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>44</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="C46" t="n">
+        <v>38</v>
       </c>
       <c r="D46" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>9</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>46</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Korea Republic</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="C47" t="n">
+        <v>55</v>
       </c>
       <c r="D47" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>8</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>47</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="C48" t="n">
+        <v>29</v>
       </c>
       <c r="D48" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>48</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Cabo Verde</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="C49" t="n">
+        <v>29</v>
       </c>
       <c r="D49" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>5</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2082,7 +1686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2141,217 +1745,186 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Fouls Against</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>23.875</v>
+        <v>38.47916666666666</v>
       </c>
       <c r="D2" t="n">
-        <v>13.91405993338347</v>
+        <v>9.660160747821894</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>12.5</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="H2" t="n">
-        <v>35</v>
+        <v>45.25</v>
       </c>
       <c r="I2" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Fouls Against</t>
+          <t>Fouls For</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>38.47916666666666</v>
+        <v>36.75</v>
       </c>
       <c r="D3" t="n">
-        <v>9.660160747821894</v>
+        <v>10.47489399733091</v>
       </c>
       <c r="E3" t="n">
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>29.75</v>
       </c>
       <c r="G3" t="n">
-        <v>37</v>
+        <v>34.5</v>
       </c>
       <c r="H3" t="n">
-        <v>45.25</v>
+        <v>43</v>
       </c>
       <c r="I3" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Fouls For</t>
+          <t>Indirect Red Cards</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>36.75</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>10.47489399733091</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>29.75</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>34.5</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Indirect Red Cards</t>
+          <t>Offsides</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>5.8125</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3.050331338821366</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Offsides</t>
+          <t>Red Cards</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>5.8125</v>
+        <v>0.25</v>
       </c>
       <c r="D6" t="n">
-        <v>3.050331338821366</v>
+        <v>0.5259237061407777</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Red Cards</t>
+          <t>Yellow Cards</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>0.25</v>
+        <v>4.145833333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5259237061407777</v>
+        <v>1.945967826080854</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Yellow Cards</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>48</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4.145833333333333</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.945967826080854</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="n">
         <v>9</v>
       </c>
     </row>

--- a/outputs/fifa_team_statistics/excel_por_categoria/Discipline.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Discipline.xlsx
@@ -557,22 +557,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1482,16 +1482,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C42" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1694,9 +1694,9 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1752,10 +1752,10 @@
         <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>38.47916666666666</v>
+        <v>38.95833333333334</v>
       </c>
       <c r="D2" t="n">
-        <v>9.660160747821894</v>
+        <v>9.673298043349071</v>
       </c>
       <c r="E2" t="n">
         <v>15</v>
@@ -1764,10 +1764,10 @@
         <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H2" t="n">
-        <v>45.25</v>
+        <v>46</v>
       </c>
       <c r="I2" t="n">
         <v>59</v>
@@ -1783,16 +1783,16 @@
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>36.75</v>
+        <v>37.20833333333334</v>
       </c>
       <c r="D3" t="n">
-        <v>10.47489399733091</v>
+        <v>9.821726531355756</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>29.75</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
         <v>34.5</v>
@@ -1845,10 +1845,10 @@
         <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>5.8125</v>
+        <v>5.958333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>3.050331338821366</v>
+        <v>3.155261282186509</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1907,10 +1907,10 @@
         <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>4.145833333333333</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="D7" t="n">
-        <v>1.945967826080854</v>
+        <v>1.949722657127498</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
